--- a/docs/data/jp/xlsx/9115.xlsx
+++ b/docs/data/jp/xlsx/9115.xlsx
@@ -7815,7 +7815,7 @@
     <row r="109">
       <c r="A109" s="18" t="inlineStr">
         <is>
-          <t>Gain On Sales Of Vessel El</t>
+          <t>선박 매각이익</t>
         </is>
       </c>
       <c r="C109" s="20" t="n">
@@ -7994,7 +7994,7 @@
     <row r="114">
       <c r="A114" s="18" t="inlineStr">
         <is>
-          <t>Loss On Sales Of Subsidiaries Stocks EL</t>
+          <t>자회사 주식 매각손실</t>
         </is>
       </c>
       <c r="F114" s="20" t="n">
@@ -8855,7 +8855,7 @@
     <row r="129">
       <c r="A129" s="18" t="inlineStr">
         <is>
-          <t>Revaluation Reserve For Land Net Of Tax OCI</t>
+          <t>토지재평가차액금</t>
         </is>
       </c>
       <c r="D129" s="20" t="n">
@@ -10941,7 +10941,7 @@
     <row r="181">
       <c r="A181" s="18" t="inlineStr">
         <is>
-          <t>Loss On Sale Of Subsidiaries Ope CF</t>
+          <t>자회사 주식 매각손실</t>
         </is>
       </c>
       <c r="I181" s="20" t="n">
@@ -11193,7 +11193,7 @@
     <row r="187">
       <c r="A187" s="18" t="inlineStr">
         <is>
-          <t>Loss Gain On Investments In Silent Partnership Ope CF</t>
+          <t>익명조합 투자손익</t>
         </is>
       </c>
       <c r="E187" s="20" t="n">
@@ -11227,7 +11227,7 @@
     <row r="188">
       <c r="A188" s="18" t="inlineStr">
         <is>
-          <t>Loss Gain On Valuation Of Derivatives Ope CF</t>
+          <t>파생상품 평가손익</t>
         </is>
       </c>
       <c r="C188" s="20" t="n">
@@ -11463,7 +11463,7 @@
     <row r="193">
       <c r="A193" s="18" t="inlineStr">
         <is>
-          <t>Increase Decrease In Provision For Special Repairs Ope CF</t>
+          <t>특별수선충당금 증감액</t>
         </is>
       </c>
       <c r="C193" s="20" t="n">
@@ -11683,7 +11683,7 @@
     <row r="197">
       <c r="A197" s="18" t="inlineStr">
         <is>
-          <t>Increase Decrease In Accounts Payable Shipping Ope CF</t>
+          <t>해운업 미지급금 증감액</t>
         </is>
       </c>
       <c r="C197" s="20" t="n">
@@ -12123,7 +12123,7 @@
     <row r="205">
       <c r="A205" s="18" t="inlineStr">
         <is>
-          <t>Net Decrease Increase In Short Term Investment Securities Inv CF</t>
+          <t>유가증권 순증감액</t>
         </is>
       </c>
       <c r="O205" s="20" t="n">
@@ -16372,7 +16372,7 @@
     <row r="77">
       <c r="A77" s="18" t="inlineStr">
         <is>
-          <t>Vessels Net</t>
+          <t>선박(순액)</t>
         </is>
       </c>
       <c r="C77" s="20" t="n">
@@ -16927,7 +16927,7 @@
     <row r="92">
       <c r="A92" s="18" t="inlineStr">
         <is>
-          <t>Accounts Payable Shipping CLWAT</t>
+          <t>해운업 미지급금</t>
         </is>
       </c>
       <c r="C92" s="20" t="n">
@@ -17336,7 +17336,7 @@
     <row r="105">
       <c r="A105" s="18" t="inlineStr">
         <is>
-          <t>Deferred Tax Liabilities For Land Revaluation</t>
+          <t>재평가 관련 이연법인세부채</t>
         </is>
       </c>
       <c r="C105" s="20" t="n">
@@ -17410,7 +17410,7 @@
     <row r="107">
       <c r="A107" s="18" t="inlineStr">
         <is>
-          <t>Provision For Special Repairs</t>
+          <t>특별수선충당금</t>
         </is>
       </c>
       <c r="C107" s="20" t="n">
@@ -17447,7 +17447,7 @@
     <row r="108">
       <c r="A108" s="18" t="inlineStr">
         <is>
-          <t>Provision NCL</t>
+          <t>충당금 계</t>
         </is>
       </c>
       <c r="C108" s="20" t="n">
@@ -17521,7 +17521,7 @@
     <row r="110">
       <c r="A110" s="18" t="inlineStr">
         <is>
-          <t>Liabilities From Application Of Equity Method NCL</t>
+          <t>지분법 적용 관련 부채</t>
         </is>
       </c>
       <c r="C110" s="20" t="n">
@@ -17928,7 +17928,7 @@
     <row r="121">
       <c r="A121" s="18" t="inlineStr">
         <is>
-          <t>Revaluation Reserve For Land</t>
+          <t>토지재평가차액금</t>
         </is>
       </c>
       <c r="C121" s="20" t="n">
